--- a/output/11_11GHz_2+0_시범비교(회신전_참고용).xlsx
+++ b/output/11_11GHz_2+0_시범비교(회신전_참고용).xlsx
@@ -804,7 +804,7 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -1198,7 +1198,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R493</t>
+          <t>K9213024</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -1701,7 +1701,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R492</t>
+          <t>K9213023</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">

--- a/output/11_11GHz_2+0_시범비교(회신전_참고용).xlsx
+++ b/output/11_11GHz_2+0_시범비교(회신전_참고용).xlsx
@@ -853,10 +853,10 @@
         <v>8</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="3">
@@ -958,10 +958,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>185407.2</v>
+        <v>177916</v>
       </c>
     </row>
     <row r="8">
@@ -1226,7 +1226,7 @@
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
     </row>
   </sheetData>
@@ -1335,10 +1335,10 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="5">
@@ -1356,10 +1356,10 @@
         <v>8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>370814.4</v>
+        <v>355832</v>
       </c>
     </row>
     <row r="6">
@@ -1461,10 +1461,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>170557.2</v>
+        <v>163664</v>
       </c>
     </row>
     <row r="11">
@@ -1813,7 +1813,7 @@
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="n">
-        <v>47709791.642</v>
+        <v>47679525.642</v>
       </c>
     </row>
   </sheetData>
@@ -1887,7 +1887,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>47709791.642</v>
+        <v>47679525.642</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
